--- a/Aule esami Polito, disposizione posti.xlsx
+++ b/Aule esami Polito, disposizione posti.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simone\OneDrive\Documenti\PoliTO\Didattica\exam-positioner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAF5CFE-C532-457A-AC7F-D26E72C6FDDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A44A63E-4C07-4AC3-8167-939B76B0963B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12240" tabRatio="719" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Aule R" sheetId="1" r:id="rId1"/>
@@ -1691,7 +1691,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:X41"/>
+  <dimension ref="A1:Y41"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="22" width="5.33203125" customWidth="1"/>
@@ -1833,29 +1833,21 @@
       </c>
       <c r="C4" s="9"/>
       <c r="D4" s="9"/>
-      <c r="E4" s="9">
-        <v>1</v>
-      </c>
+      <c r="E4" s="9"/>
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="9">
-        <v>1</v>
-      </c>
+      <c r="I4" s="9"/>
       <c r="J4" s="9"/>
       <c r="K4" s="9"/>
       <c r="L4" s="12"/>
       <c r="M4" s="9"/>
       <c r="N4" s="9"/>
-      <c r="O4" s="9">
-        <v>1</v>
-      </c>
+      <c r="O4" s="9"/>
       <c r="P4" s="9"/>
       <c r="Q4" s="9"/>
       <c r="R4" s="9"/>
-      <c r="S4" s="9">
-        <v>1</v>
-      </c>
+      <c r="S4" s="9"/>
       <c r="T4" s="9"/>
       <c r="U4" s="9"/>
     </row>
@@ -1911,9 +1903,7 @@
       <c r="F6" s="10"/>
       <c r="G6" s="10"/>
       <c r="H6" s="9"/>
-      <c r="I6" s="9">
-        <v>1</v>
-      </c>
+      <c r="I6" s="9"/>
       <c r="J6" s="9"/>
       <c r="K6" s="9"/>
       <c r="L6" s="12"/>
@@ -1975,29 +1965,21 @@
       </c>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
-      <c r="E8" s="10">
-        <v>1</v>
-      </c>
+      <c r="E8" s="10"/>
       <c r="F8" s="10"/>
       <c r="G8" s="10"/>
       <c r="H8" s="9"/>
-      <c r="I8" s="9">
-        <v>1</v>
-      </c>
+      <c r="I8" s="9"/>
       <c r="J8" s="9"/>
       <c r="K8" s="9"/>
       <c r="L8" s="12"/>
       <c r="M8" s="9"/>
       <c r="N8" s="9"/>
-      <c r="O8" s="9">
-        <v>1</v>
-      </c>
+      <c r="O8" s="9"/>
       <c r="P8" s="10"/>
       <c r="Q8" s="10"/>
       <c r="R8" s="10"/>
-      <c r="S8" s="10">
-        <v>1</v>
-      </c>
+      <c r="S8" s="10"/>
       <c r="T8" s="10"/>
       <c r="U8" s="9"/>
     </row>
@@ -2181,7 +2163,7 @@
       </c>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
-      <c r="E14" s="10"/>
+      <c r="E14" s="9"/>
       <c r="F14" s="10"/>
       <c r="G14" s="9"/>
       <c r="H14" s="9"/>
@@ -2195,7 +2177,7 @@
       <c r="P14" s="9"/>
       <c r="Q14" s="9"/>
       <c r="R14" s="9"/>
-      <c r="S14" s="10"/>
+      <c r="S14" s="9"/>
       <c r="T14" s="9"/>
       <c r="U14" s="9"/>
     </row>
@@ -2261,7 +2243,7 @@
       <c r="P16" s="9"/>
       <c r="Q16" s="9"/>
       <c r="R16" s="9"/>
-      <c r="S16" s="10"/>
+      <c r="S16" s="9"/>
       <c r="T16" s="9"/>
       <c r="U16" s="9"/>
     </row>
@@ -2506,7 +2488,7 @@
       </c>
       <c r="E24" s="13">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F24" s="13">
         <f t="shared" si="0"/>
@@ -2522,7 +2504,7 @@
       </c>
       <c r="I24" s="13">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J24" s="13">
         <f t="shared" si="0"/>
@@ -2546,7 +2528,7 @@
       </c>
       <c r="O24" s="12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P24" s="12">
         <f t="shared" si="0"/>
@@ -2562,7 +2544,7 @@
       </c>
       <c r="S24" s="12">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="T24" s="12">
         <f t="shared" si="0"/>
@@ -2578,7 +2560,7 @@
       </c>
       <c r="X24" s="4">
         <f>SUM(C24:V24)</f>
-        <v>63</v>
+        <v>54</v>
       </c>
     </row>
     <row r="25" spans="1:24" ht="13.8">
@@ -2865,7 +2847,7 @@
       <c r="W32" s="3"/>
       <c r="X32" s="4"/>
     </row>
-    <row r="33" spans="1:24" ht="13.8">
+    <row r="33" spans="1:25" ht="13.8">
       <c r="A33" s="1">
         <v>0</v>
       </c>
@@ -2895,7 +2877,7 @@
       <c r="W33" s="3"/>
       <c r="X33" s="4"/>
     </row>
-    <row r="34" spans="1:24" ht="13.8">
+    <row r="34" spans="1:25" ht="13.8">
       <c r="A34" s="1">
         <v>0</v>
       </c>
@@ -2935,7 +2917,7 @@
       <c r="W34" s="3"/>
       <c r="X34" s="4"/>
     </row>
-    <row r="35" spans="1:24" ht="13.8">
+    <row r="35" spans="1:25" ht="13.8">
       <c r="A35" s="1">
         <v>0</v>
       </c>
@@ -2965,7 +2947,7 @@
       <c r="W35" s="3"/>
       <c r="X35" s="4"/>
     </row>
-    <row r="36" spans="1:24" ht="13.8">
+    <row r="36" spans="1:25" ht="13.8">
       <c r="A36" s="1">
         <v>0</v>
       </c>
@@ -3005,7 +2987,7 @@
       <c r="W36" s="3"/>
       <c r="X36" s="4"/>
     </row>
-    <row r="37" spans="1:24" ht="13.8">
+    <row r="37" spans="1:25" ht="13.8">
       <c r="A37" s="1">
         <v>0</v>
       </c>
@@ -3034,8 +3016,12 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
       <c r="X37" s="4"/>
-    </row>
-    <row r="38" spans="1:24" ht="13.8">
+      <c r="Y37">
+        <f>X41*4 + X24*4</f>
+        <v>316</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" ht="13.8">
       <c r="A38" s="1">
         <v>0</v>
       </c>
@@ -3075,7 +3061,7 @@
       <c r="W38" s="3"/>
       <c r="X38" s="4"/>
     </row>
-    <row r="39" spans="1:24" ht="13.8">
+    <row r="39" spans="1:25" ht="13.8">
       <c r="A39" s="1">
         <v>0</v>
       </c>
@@ -3103,7 +3089,7 @@
       <c r="W39" s="3"/>
       <c r="X39" s="4"/>
     </row>
-    <row r="40" spans="1:24" ht="13.8">
+    <row r="40" spans="1:25" ht="13.8">
       <c r="A40" s="1">
         <v>0</v>
       </c>
@@ -3133,7 +3119,7 @@
       <c r="W40" s="3"/>
       <c r="X40" s="4"/>
     </row>
-    <row r="41" spans="1:24" ht="13.8">
+    <row r="41" spans="1:25" ht="13.8">
       <c r="A41" s="1">
         <v>0</v>
       </c>
